--- a/data.mn/public/datasets/cpi-national-monthly.xlsx
+++ b/data.mn/public/datasets/cpi-national-monthly.xlsx
@@ -414,12 +414,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2421,6 +2417,26 @@
       </c>
       <c r="B200" t="n">
         <v>179.3</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>180.4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>181.1</v>
       </c>
     </row>
   </sheetData>
@@ -2434,12 +2450,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4441,6 +4453,26 @@
       </c>
       <c r="B200" t="n">
         <v>179.3</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>180.4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>181.1</v>
       </c>
     </row>
   </sheetData>
